--- a/docs/data/jp/xlsx/5834.xlsx
+++ b/docs/data/jp/xlsx/5834.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC162"/>
+  <dimension ref="A1:AC169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4171,10 +4174,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>2565</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4209,7 +4214,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>15934000</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5408,7 +5415,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5657,1385 +5664,1405 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>11564</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>6143</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>16960</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>267</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>15419</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>9036</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>6740</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>6489</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>12260</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>19569</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>12015</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>16989</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>16841</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>16960</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>6740</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>12015</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>2191</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>2109</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>2235</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>2203</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>2492</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>2847</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>2912</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>3930</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>3694</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>3665</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>2635</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>5269</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>3005</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>2235</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>2912</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>2635</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>666</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>788</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>846</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>980</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>731</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>1014</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>1358</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>965</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>988</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>882</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>1306</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>852</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>846</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>1014</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>882</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>1526</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>1321</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>1389</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>1223</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>1761</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>1846</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>1898</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>2571</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>2729</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>2677</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>1753</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>3963</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>2153</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>1389</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>1898</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>1753</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
-        </is>
+          <t>판매비와 관리비</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="n">
+        <v>666</v>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>788</v>
+      </c>
+      <c r="E83" s="22" t="n">
+        <v>846</v>
+      </c>
+      <c r="F83" s="22" t="n">
+        <v>980</v>
+      </c>
+      <c r="G83" s="22" t="n">
+        <v>731</v>
+      </c>
+      <c r="H83" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I83" s="22" t="n">
+        <v>1014</v>
+      </c>
+      <c r="J83" s="22" t="n">
+        <v>1358</v>
+      </c>
+      <c r="K83" s="22" t="n">
+        <v>965</v>
+      </c>
+      <c r="L83" s="22" t="n">
+        <v>988</v>
+      </c>
+      <c r="M83" s="22" t="n">
+        <v>882</v>
+      </c>
+      <c r="N83" s="22" t="n">
+        <v>1306</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>0</v>
+        <v>852</v>
+      </c>
+      <c r="V83" s="22" t="n">
+        <v>846</v>
+      </c>
+      <c r="W83" s="22" t="n">
+        <v>1014</v>
+      </c>
+      <c r="X83" s="22" t="n">
+        <v>882</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>18</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>1526</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>1321</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>1389</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>1223</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>1761</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>1846</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>1898</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>2571</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>2729</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>2677</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>1753</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>3963</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>2153</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>1389</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>1898</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>1753</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>Gain On Sale Of Equity Underwritten NOI</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>53</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>58</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>136</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>70</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>112</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>120</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>140</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>120</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>58</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>187</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>58</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>120</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>58</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>-9</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>19</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>-19</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>12</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" s="22" t="n">
-        <v>0</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="U87" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" s="22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>127</v>
+        <v>6</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>136</v>
+        <v>14</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="U88" s="22" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="V88" s="22" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>127</v>
+        <v>6</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>88</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>Gain On Sale Of Equity Underwritten NOI</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>191</v>
+        <v>70</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>242</v>
+        <v>112</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>282</v>
+        <v>120</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>295</v>
+        <v>140</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>303</v>
+        <v>120</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>332</v>
+        <v>58</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>336</v>
+        <v>187</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>282</v>
+        <v>120</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>332</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="D90" s="22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="G90" s="22" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M90" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="N90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="E90" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="F90" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="G90" s="22" t="n">
-        <v>70</v>
-      </c>
-      <c r="H90" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="I90" s="22" t="n">
-        <v>68</v>
-      </c>
-      <c r="J90" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="K90" s="22" t="n">
-        <v>77</v>
-      </c>
-      <c r="L90" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="M90" s="22" t="n">
-        <v>137</v>
-      </c>
-      <c r="N90" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="U90" s="22" t="n">
-        <v>39</v>
-      </c>
       <c r="V90" s="22" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>137</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>주식교부비</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="E91" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="F91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="U91" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V91" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="W91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>사채발행비</t>
-        </is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="E92" s="22" t="n">
+        <v>63</v>
+      </c>
+      <c r="F92" s="22" t="n">
+        <v>156</v>
+      </c>
+      <c r="G92" s="22" t="n">
+        <v>51</v>
+      </c>
+      <c r="H92" s="22" t="n">
+        <v>113</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>26</v>
+        <v>127</v>
+      </c>
+      <c r="J92" s="22" t="n">
+        <v>143</v>
+      </c>
+      <c r="K92" s="22" t="n">
+        <v>136</v>
+      </c>
+      <c r="L92" s="22" t="n">
+        <v>98</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="N92" s="22" t="n">
+        <v>188</v>
+      </c>
+      <c r="U92" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="V92" s="22" t="n">
+        <v>63</v>
       </c>
       <c r="W92" s="22" t="n">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="n">
+        <v>104</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>0</v>
+        <v>145</v>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>162</v>
+      </c>
+      <c r="G93" s="22" t="n">
+        <v>191</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>6</v>
+        <v>242</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>16</v>
+        <v>282</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>295</v>
+      </c>
+      <c r="K93" s="22" t="n">
+        <v>303</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>0</v>
+        <v>332</v>
+      </c>
+      <c r="N93" s="22" t="n">
+        <v>336</v>
+      </c>
+      <c r="U93" s="22" t="n">
+        <v>99</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>16</v>
+        <v>282</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>지급수수료</t>
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>70</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="K94" s="22" t="n">
+        <v>77</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>0</v>
+        <v>137</v>
+      </c>
+      <c r="N94" s="22" t="n">
+        <v>16</v>
       </c>
       <c r="U94" s="22" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="V94" s="22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W94" s="22" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X94" s="22" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
-        </is>
-      </c>
-      <c r="C95" s="22" t="n">
-        <v>167</v>
-      </c>
-      <c r="D95" s="22" t="n">
-        <v>147</v>
+          <t>주식교부비</t>
+        </is>
       </c>
       <c r="E95" s="22" t="n">
-        <v>175</v>
-      </c>
-      <c r="F95" s="22" t="n">
-        <v>171</v>
-      </c>
-      <c r="G95" s="22" t="n">
-        <v>272</v>
-      </c>
-      <c r="H95" s="22" t="n">
-        <v>255</v>
-      </c>
-      <c r="I95" s="22" t="n">
-        <v>393</v>
-      </c>
-      <c r="J95" s="22" t="n">
-        <v>318</v>
-      </c>
-      <c r="K95" s="22" t="n">
-        <v>381</v>
-      </c>
-      <c r="L95" s="22" t="n">
-        <v>346</v>
-      </c>
-      <c r="M95" s="22" t="n">
-        <v>469</v>
-      </c>
-      <c r="N95" s="22" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="U95" s="22" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>175</v>
-      </c>
-      <c r="W95" s="22" t="n">
-        <v>393</v>
-      </c>
-      <c r="X95" s="22" t="n">
-        <v>469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="n">
-        <v>1396</v>
-      </c>
-      <c r="D96" s="12" t="n">
-        <v>1219</v>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>1277</v>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>1207</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>1541</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>1705</v>
-      </c>
-      <c r="I96" s="12" t="n">
-        <v>1631</v>
-      </c>
-      <c r="J96" s="12" t="n">
-        <v>2397</v>
-      </c>
-      <c r="K96" s="12" t="n">
-        <v>2483</v>
-      </c>
-      <c r="L96" s="12" t="n">
-        <v>2429</v>
-      </c>
-      <c r="M96" s="12" t="n">
-        <v>1372</v>
-      </c>
-      <c r="N96" s="12" t="n">
-        <v>3798</v>
-      </c>
-      <c r="U96" s="12" t="n">
-        <v>2050</v>
-      </c>
-      <c r="V96" s="12" t="n">
-        <v>1277</v>
-      </c>
-      <c r="W96" s="12" t="n">
-        <v>1631</v>
-      </c>
-      <c r="X96" s="12" t="n">
-        <v>1372</v>
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>사채발행비</t>
+        </is>
+      </c>
+      <c r="I96" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="X96" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>관계회사 청산손실</t>
-        </is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="E97" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U97" s="22" t="n">
+      <c r="H97" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V97" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="W97" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="X97" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="H98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="U98" s="22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V98" s="22" t="n">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="W98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="n">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="n">
+        <v>167</v>
+      </c>
+      <c r="D99" s="22" t="n">
+        <v>147</v>
+      </c>
+      <c r="E99" s="22" t="n">
+        <v>175</v>
+      </c>
+      <c r="F99" s="22" t="n">
+        <v>171</v>
+      </c>
+      <c r="G99" s="22" t="n">
+        <v>272</v>
+      </c>
+      <c r="H99" s="22" t="n">
+        <v>255</v>
+      </c>
+      <c r="I99" s="22" t="n">
+        <v>393</v>
+      </c>
+      <c r="J99" s="22" t="n">
+        <v>318</v>
+      </c>
+      <c r="K99" s="22" t="n">
+        <v>381</v>
+      </c>
+      <c r="L99" s="22" t="n">
+        <v>346</v>
+      </c>
+      <c r="M99" s="22" t="n">
+        <v>469</v>
+      </c>
+      <c r="N99" s="22" t="n">
+        <v>352</v>
+      </c>
+      <c r="U99" s="22" t="n">
+        <v>137</v>
+      </c>
+      <c r="V99" s="22" t="n">
+        <v>175</v>
+      </c>
+      <c r="W99" s="22" t="n">
+        <v>393</v>
+      </c>
+      <c r="X99" s="22" t="n">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="n">
         <v>1396</v>
       </c>
-      <c r="D99" s="12" t="n">
+      <c r="D100" s="12" t="n">
         <v>1219</v>
       </c>
-      <c r="E99" s="12" t="n">
-        <v>1242</v>
-      </c>
-      <c r="F99" s="12" t="n">
+      <c r="E100" s="12" t="n">
+        <v>1277</v>
+      </c>
+      <c r="F100" s="12" t="n">
         <v>1207</v>
       </c>
-      <c r="G99" s="12" t="n">
+      <c r="G100" s="12" t="n">
         <v>1541</v>
       </c>
-      <c r="H99" s="12" t="n">
+      <c r="H100" s="12" t="n">
         <v>1705</v>
       </c>
-      <c r="I99" s="12" t="n">
-        <v>1612</v>
-      </c>
-      <c r="J99" s="12" t="n">
+      <c r="I100" s="12" t="n">
+        <v>1631</v>
+      </c>
+      <c r="J100" s="12" t="n">
         <v>2397</v>
       </c>
-      <c r="K99" s="12" t="n">
+      <c r="K100" s="12" t="n">
         <v>2483</v>
       </c>
-      <c r="L99" s="12" t="n">
+      <c r="L100" s="12" t="n">
         <v>2429</v>
       </c>
-      <c r="M99" s="12" t="n">
-        <v>1343</v>
-      </c>
-      <c r="N99" s="12" t="n">
+      <c r="M100" s="12" t="n">
+        <v>1372</v>
+      </c>
+      <c r="N100" s="12" t="n">
         <v>3798</v>
       </c>
-      <c r="U99" s="12" t="n">
-        <v>2037</v>
-      </c>
-      <c r="V99" s="12" t="n">
-        <v>1242</v>
-      </c>
-      <c r="W99" s="12" t="n">
-        <v>1612</v>
-      </c>
-      <c r="X99" s="12" t="n">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>법인세·주민세·사업세</t>
-        </is>
-      </c>
-      <c r="C100" s="22" t="n">
-        <v>268</v>
-      </c>
-      <c r="D100" s="22" t="n">
-        <v>689</v>
-      </c>
-      <c r="E100" s="22" t="n">
-        <v>675</v>
-      </c>
-      <c r="F100" s="22" t="n">
-        <v>519</v>
-      </c>
-      <c r="G100" s="22" t="n">
-        <v>759</v>
-      </c>
-      <c r="H100" s="22" t="n">
-        <v>704</v>
-      </c>
-      <c r="I100" s="22" t="n">
-        <v>669</v>
-      </c>
-      <c r="J100" s="22" t="n">
-        <v>786</v>
-      </c>
-      <c r="K100" s="22" t="n">
-        <v>758</v>
-      </c>
-      <c r="L100" s="22" t="n">
-        <v>1113</v>
-      </c>
-      <c r="M100" s="22" t="n">
-        <v>1174</v>
-      </c>
-      <c r="N100" s="22" t="n">
-        <v>702</v>
-      </c>
-      <c r="U100" s="22" t="n">
-        <v>1324</v>
-      </c>
-      <c r="V100" s="22" t="n">
-        <v>675</v>
-      </c>
-      <c r="W100" s="22" t="n">
-        <v>669</v>
-      </c>
-      <c r="X100" s="22" t="n">
-        <v>1174</v>
+      <c r="U100" s="12" t="n">
+        <v>2050</v>
+      </c>
+      <c r="V100" s="12" t="n">
+        <v>1277</v>
+      </c>
+      <c r="W100" s="12" t="n">
+        <v>1631</v>
+      </c>
+      <c r="X100" s="12" t="n">
+        <v>1372</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C101" s="22" t="n">
-        <v>151</v>
-      </c>
-      <c r="D101" s="22" t="n">
-        <v>-326</v>
-      </c>
-      <c r="E101" s="22" t="n">
-        <v>-296</v>
-      </c>
-      <c r="F101" s="22" t="n">
-        <v>-129</v>
-      </c>
-      <c r="G101" s="22" t="n">
-        <v>-302</v>
-      </c>
-      <c r="H101" s="22" t="n">
-        <v>-187</v>
-      </c>
-      <c r="I101" s="22" t="n">
-        <v>-356</v>
-      </c>
-      <c r="J101" s="22" t="n">
-        <v>42</v>
-      </c>
-      <c r="K101" s="22" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L101" s="22" t="n">
-        <v>-383</v>
-      </c>
-      <c r="M101" s="22" t="n">
-        <v>-878</v>
-      </c>
-      <c r="N101" s="22" t="n">
-        <v>555</v>
-      </c>
-      <c r="U101" s="22" t="n">
-        <v>-710</v>
-      </c>
-      <c r="V101" s="22" t="n">
-        <v>-296</v>
-      </c>
-      <c r="W101" s="22" t="n">
-        <v>-356</v>
-      </c>
-      <c r="X101" s="22" t="n">
-        <v>-878</v>
+      <c r="A101" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G101" s="17">
+        <f>IF(OR(G100="",C100=""),"",IF(C100&lt;=0,"",IFERROR(G100/C100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H101" s="17">
+        <f>IF(OR(H100="",D100=""),"",IF(D100&lt;=0,"",IFERROR(H100/D100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I101" s="17">
+        <f>IF(OR(I100="",E100=""),"",IF(E100&lt;=0,"",IFERROR(I100/E100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J101" s="17">
+        <f>IF(OR(J100="",F100=""),"",IF(F100&lt;=0,"",IFERROR(J100/F100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K101" s="17">
+        <f>IF(OR(K100="",G100=""),"",IF(G100&lt;=0,"",IFERROR(K100/G100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L101" s="17">
+        <f>IF(OR(L100="",H100=""),"",IF(H100&lt;=0,"",IFERROR(L100/H100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M101" s="17">
+        <f>IF(OR(M100="",I100=""),"",IF(I100&lt;=0,"",IFERROR(M100/I100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N101" s="17">
+        <f>IF(OR(N100="",J100=""),"",IF(J100&lt;=0,"",IFERROR(N100/J100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U101" s="17">
+        <f>IF(OR(U100="",T100=""),"",IF(T100&lt;=0,"",IFERROR(U100/T100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V101" s="17">
+        <f>IF(OR(V100="",U100=""),"",IF(U100&lt;=0,"",IFERROR(V100/U100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W101" s="17">
+        <f>IF(OR(W100="",V100=""),"",IF(V100&lt;=0,"",IFERROR(W100/V100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X101" s="17">
+        <f>IF(OR(X100="",W100=""),"",IF(W100&lt;=0,"",IFERROR(X100/W100-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="n">
-        <v>420</v>
-      </c>
-      <c r="D102" s="22" t="n">
-        <v>361</v>
+          <t>관계회사 청산손실</t>
+        </is>
       </c>
       <c r="E102" s="22" t="n">
-        <v>379</v>
-      </c>
-      <c r="F102" s="22" t="n">
-        <v>389</v>
-      </c>
-      <c r="G102" s="22" t="n">
-        <v>457</v>
-      </c>
-      <c r="H102" s="22" t="n">
-        <v>518</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>312</v>
-      </c>
-      <c r="J102" s="22" t="n">
-        <v>828</v>
-      </c>
-      <c r="K102" s="22" t="n">
-        <v>747</v>
-      </c>
-      <c r="L102" s="22" t="n">
-        <v>729</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>296</v>
-      </c>
-      <c r="N102" s="22" t="n">
-        <v>1257</v>
+        <v>0</v>
       </c>
       <c r="U102" s="22" t="n">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="V102" s="22" t="n">
-        <v>379</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>312</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n">
-        <v>976</v>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>858</v>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>862</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>817</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>1085</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>1186</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>1568</v>
-      </c>
-      <c r="K103" s="12" t="n">
-        <v>1736</v>
-      </c>
-      <c r="L103" s="12" t="n">
-        <v>1701</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>1046</v>
-      </c>
-      <c r="N103" s="12" t="n">
-        <v>2541</v>
-      </c>
-      <c r="U103" s="12" t="n">
-        <v>1423</v>
-      </c>
-      <c r="V103" s="12" t="n">
-        <v>862</v>
-      </c>
-      <c r="W103" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="X103" s="12" t="n">
-        <v>1046</v>
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="E103" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="U103" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="V103" s="22" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>지배주주 순이익</t>
+          <t>법인세차감전 순이익</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>976</v>
+        <v>1396</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>858</v>
+        <v>1219</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>862</v>
+        <v>1242</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>817</v>
+        <v>1207</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1085</v>
+        <v>1541</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1186</v>
+        <v>1705</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>1300</v>
+        <v>1612</v>
       </c>
       <c r="J104" s="12" t="n">
-        <v>1568</v>
+        <v>2397</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>1736</v>
+        <v>2483</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>1701</v>
+        <v>2429</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>1046</v>
+        <v>1343</v>
       </c>
       <c r="N104" s="12" t="n">
-        <v>2541</v>
+        <v>3798</v>
       </c>
       <c r="U104" s="12" t="n">
-        <v>1423</v>
+        <v>2037</v>
       </c>
       <c r="V104" s="12" t="n">
-        <v>862</v>
+        <v>1242</v>
       </c>
       <c r="W104" s="12" t="n">
-        <v>1300</v>
+        <v>1612</v>
       </c>
       <c r="X104" s="12" t="n">
-        <v>1046</v>
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="n">
+        <v>268</v>
+      </c>
+      <c r="D105" s="22" t="n">
+        <v>689</v>
+      </c>
+      <c r="E105" s="22" t="n">
+        <v>675</v>
+      </c>
+      <c r="F105" s="22" t="n">
+        <v>519</v>
+      </c>
+      <c r="G105" s="22" t="n">
+        <v>759</v>
+      </c>
+      <c r="H105" s="22" t="n">
+        <v>704</v>
+      </c>
+      <c r="I105" s="22" t="n">
+        <v>669</v>
+      </c>
+      <c r="J105" s="22" t="n">
+        <v>786</v>
+      </c>
+      <c r="K105" s="22" t="n">
+        <v>758</v>
+      </c>
+      <c r="L105" s="22" t="n">
+        <v>1113</v>
+      </c>
+      <c r="M105" s="22" t="n">
+        <v>1174</v>
+      </c>
+      <c r="N105" s="22" t="n">
+        <v>702</v>
+      </c>
+      <c r="U105" s="22" t="n">
+        <v>1324</v>
+      </c>
+      <c r="V105" s="22" t="n">
+        <v>675</v>
+      </c>
+      <c r="W105" s="22" t="n">
+        <v>669</v>
+      </c>
+      <c r="X105" s="22" t="n">
+        <v>1174</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B106" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="n"/>
-      <c r="D106" s="18" t="n"/>
-      <c r="E106" s="18" t="n"/>
-      <c r="F106" s="18" t="n"/>
-      <c r="G106" s="18" t="n"/>
-      <c r="H106" s="18" t="n"/>
-      <c r="I106" s="18" t="n"/>
-      <c r="J106" s="18" t="n"/>
-      <c r="K106" s="18" t="n"/>
-      <c r="L106" s="18" t="n"/>
-      <c r="M106" s="18" t="n"/>
-      <c r="N106" s="18" t="n"/>
-      <c r="O106" s="18" t="n"/>
-      <c r="P106" s="18" t="n"/>
-      <c r="Q106" s="18" t="n"/>
-      <c r="R106" s="18" t="n"/>
-      <c r="S106" s="18" t="n"/>
-      <c r="T106" s="18" t="n"/>
-      <c r="U106" s="18" t="n"/>
-      <c r="V106" s="18" t="n"/>
-      <c r="W106" s="18" t="n"/>
-      <c r="X106" s="18" t="n"/>
-      <c r="Y106" s="18" t="n"/>
-      <c r="Z106" s="18" t="n"/>
-      <c r="AA106" s="18" t="n"/>
-      <c r="AB106" s="18" t="n"/>
-      <c r="AC106" s="18" t="n"/>
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="n">
+        <v>151</v>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>-326</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>-296</v>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>-302</v>
+      </c>
+      <c r="H106" s="22" t="n">
+        <v>-187</v>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>-356</v>
+      </c>
+      <c r="J106" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="K106" s="22" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L106" s="22" t="n">
+        <v>-383</v>
+      </c>
+      <c r="M106" s="22" t="n">
+        <v>-878</v>
+      </c>
+      <c r="N106" s="22" t="n">
+        <v>555</v>
+      </c>
+      <c r="U106" s="22" t="n">
+        <v>-710</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>-296</v>
+      </c>
+      <c r="W106" s="22" t="n">
+        <v>-356</v>
+      </c>
+      <c r="X106" s="22" t="n">
+        <v>-878</v>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H107" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I107" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J107" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L107" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M107" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N107" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O107" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P107" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q107" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R107" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S107" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T107" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U107" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V107" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W107" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X107" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y107" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z107" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA107" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB107" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC107" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="n">
+        <v>420</v>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>361</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>379</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>389</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>457</v>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>518</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>312</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>828</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>747</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>729</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>296</v>
+      </c>
+      <c r="N107" s="22" t="n">
+        <v>1257</v>
+      </c>
+      <c r="U107" s="22" t="n">
+        <v>614</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>379</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>312</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>296</v>
       </c>
     </row>
     <row r="108">
@@ -7094,1961 +7121,2377 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="20" t="inlineStr">
+      <c r="A109" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G109" s="17">
+        <f>IF(OR(G108="",C108=""),"",IF(C108&lt;=0,"",IFERROR(G108/C108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H109" s="17">
+        <f>IF(OR(H108="",D108=""),"",IF(D108&lt;=0,"",IFERROR(H108/D108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I109" s="17">
+        <f>IF(OR(I108="",E108=""),"",IF(E108&lt;=0,"",IFERROR(I108/E108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J109" s="17">
+        <f>IF(OR(J108="",F108=""),"",IF(F108&lt;=0,"",IFERROR(J108/F108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>IF(OR(K108="",G108=""),"",IF(G108&lt;=0,"",IFERROR(K108/G108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L109" s="17">
+        <f>IF(OR(L108="",H108=""),"",IF(H108&lt;=0,"",IFERROR(L108/H108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M109" s="17">
+        <f>IF(OR(M108="",I108=""),"",IF(I108&lt;=0,"",IFERROR(M108/I108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N109" s="17">
+        <f>IF(OR(N108="",J108=""),"",IF(J108&lt;=0,"",IFERROR(N108/J108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U109" s="17">
+        <f>IF(OR(U108="",T108=""),"",IF(T108&lt;=0,"",IFERROR(U108/T108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V109" s="17">
+        <f>IF(OR(V108="",U108=""),"",IF(U108&lt;=0,"",IFERROR(V108/U108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W109" s="17">
+        <f>IF(OR(W108="",V108=""),"",IF(V108&lt;=0,"",IFERROR(W108/V108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X109" s="17">
+        <f>IF(OR(X108="",W108=""),"",IF(W108&lt;=0,"",IFERROR(X108/W108-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="n">
+        <v>976</v>
+      </c>
+      <c r="D110" s="12" t="n">
+        <v>858</v>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>862</v>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>817</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>1085</v>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>1186</v>
+      </c>
+      <c r="I110" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J110" s="12" t="n">
+        <v>1568</v>
+      </c>
+      <c r="K110" s="12" t="n">
+        <v>1736</v>
+      </c>
+      <c r="L110" s="12" t="n">
+        <v>1701</v>
+      </c>
+      <c r="M110" s="12" t="n">
+        <v>1046</v>
+      </c>
+      <c r="N110" s="12" t="n">
+        <v>2541</v>
+      </c>
+      <c r="U110" s="12" t="n">
+        <v>1423</v>
+      </c>
+      <c r="V110" s="12" t="n">
+        <v>862</v>
+      </c>
+      <c r="W110" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="X110" s="12" t="n">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G111" s="17">
+        <f>IF(OR(G110="",C110=""),"",IF(C110&lt;=0,"",IFERROR(G110/C110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H111" s="17">
+        <f>IF(OR(H110="",D110=""),"",IF(D110&lt;=0,"",IFERROR(H110/D110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I111" s="17">
+        <f>IF(OR(I110="",E110=""),"",IF(E110&lt;=0,"",IFERROR(I110/E110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J111" s="17">
+        <f>IF(OR(J110="",F110=""),"",IF(F110&lt;=0,"",IFERROR(J110/F110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF(OR(K110="",G110=""),"",IF(G110&lt;=0,"",IFERROR(K110/G110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L111" s="17">
+        <f>IF(OR(L110="",H110=""),"",IF(H110&lt;=0,"",IFERROR(L110/H110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M111" s="17">
+        <f>IF(OR(M110="",I110=""),"",IF(I110&lt;=0,"",IFERROR(M110/I110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N111" s="17">
+        <f>IF(OR(N110="",J110=""),"",IF(J110&lt;=0,"",IFERROR(N110/J110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U111" s="17">
+        <f>IF(OR(U110="",T110=""),"",IF(T110&lt;=0,"",IFERROR(U110/T110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V111" s="17">
+        <f>IF(OR(V110="",U110=""),"",IF(U110&lt;=0,"",IFERROR(V110/U110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W111" s="17">
+        <f>IF(OR(W110="",V110=""),"",IF(V110&lt;=0,"",IFERROR(W110/V110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X111" s="17">
+        <f>IF(OR(X110="",W110=""),"",IF(W110&lt;=0,"",IFERROR(X110/W110-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B113" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="n"/>
+      <c r="D113" s="18" t="n"/>
+      <c r="E113" s="18" t="n"/>
+      <c r="F113" s="18" t="n"/>
+      <c r="G113" s="18" t="n"/>
+      <c r="H113" s="18" t="n"/>
+      <c r="I113" s="18" t="n"/>
+      <c r="J113" s="18" t="n"/>
+      <c r="K113" s="18" t="n"/>
+      <c r="L113" s="18" t="n"/>
+      <c r="M113" s="18" t="n"/>
+      <c r="N113" s="18" t="n"/>
+      <c r="O113" s="18" t="n"/>
+      <c r="P113" s="18" t="n"/>
+      <c r="Q113" s="18" t="n"/>
+      <c r="R113" s="18" t="n"/>
+      <c r="S113" s="18" t="n"/>
+      <c r="T113" s="18" t="n"/>
+      <c r="U113" s="18" t="n"/>
+      <c r="V113" s="18" t="n"/>
+      <c r="W113" s="18" t="n"/>
+      <c r="X113" s="18" t="n"/>
+      <c r="Y113" s="18" t="n"/>
+      <c r="Z113" s="18" t="n"/>
+      <c r="AA113" s="18" t="n"/>
+      <c r="AB113" s="18" t="n"/>
+      <c r="AC113" s="18" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N114" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O114" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P114" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q114" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R114" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S114" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T114" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U114" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V114" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W114" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X114" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y114" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z114" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA114" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB114" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC114" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="n">
+        <v>976</v>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>858</v>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>862</v>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>817</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>1085</v>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>1186</v>
+      </c>
+      <c r="I115" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J115" s="12" t="n">
+        <v>1568</v>
+      </c>
+      <c r="K115" s="12" t="n">
+        <v>1736</v>
+      </c>
+      <c r="L115" s="12" t="n">
+        <v>1701</v>
+      </c>
+      <c r="M115" s="12" t="n">
+        <v>1046</v>
+      </c>
+      <c r="N115" s="12" t="n">
+        <v>2541</v>
+      </c>
+      <c r="U115" s="12" t="n">
+        <v>1423</v>
+      </c>
+      <c r="V115" s="12" t="n">
+        <v>862</v>
+      </c>
+      <c r="W115" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="X115" s="12" t="n">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
         <is>
           <t>이연헤지손익</t>
         </is>
       </c>
-      <c r="C109" s="22" t="n">
+      <c r="C116" s="22" t="n">
         <v>145</v>
       </c>
-      <c r="D109" s="22" t="n">
+      <c r="D116" s="22" t="n">
         <v>651</v>
       </c>
-      <c r="E109" s="22" t="n">
+      <c r="E116" s="22" t="n">
         <v>-655</v>
       </c>
-      <c r="F109" s="22" t="n">
+      <c r="F116" s="22" t="n">
         <v>-404</v>
       </c>
-      <c r="G109" s="22" t="n">
+      <c r="G116" s="22" t="n">
         <v>788</v>
       </c>
-      <c r="H109" s="22" t="n">
+      <c r="H116" s="22" t="n">
         <v>-1422</v>
       </c>
-      <c r="I109" s="22" t="n">
+      <c r="I116" s="22" t="n">
         <v>1221</v>
       </c>
-      <c r="J109" s="22" t="n">
+      <c r="J116" s="22" t="n">
         <v>162</v>
       </c>
-      <c r="K109" s="22" t="n">
+      <c r="K116" s="22" t="n">
         <v>-881</v>
       </c>
-      <c r="L109" s="22" t="n">
+      <c r="L116" s="22" t="n">
         <v>-502</v>
       </c>
-      <c r="M109" s="22" t="n">
+      <c r="M116" s="22" t="n">
         <v>245</v>
       </c>
-      <c r="N109" s="22" t="n">
+      <c r="N116" s="22" t="n">
         <v>697</v>
       </c>
-      <c r="U109" s="22" t="n">
+      <c r="U116" s="22" t="n">
         <v>-257</v>
       </c>
-      <c r="V109" s="22" t="n">
+      <c r="V116" s="22" t="n">
         <v>-655</v>
       </c>
-      <c r="W109" s="22" t="n">
+      <c r="W116" s="22" t="n">
         <v>1221</v>
       </c>
-      <c r="X109" s="22" t="n">
+      <c r="X116" s="22" t="n">
         <v>245</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
         <is>
           <t>해외사업환산조정</t>
         </is>
       </c>
-      <c r="C110" s="22" t="n">
+      <c r="C117" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="22" t="n">
+      <c r="D117" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="22" t="n">
+      <c r="E117" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U110" s="22" t="n">
+      <c r="U117" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="22" t="n">
+      <c r="V117" s="22" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C111" s="22" t="n">
-        <v>145</v>
-      </c>
-      <c r="D111" s="22" t="n">
-        <v>651</v>
-      </c>
-      <c r="E111" s="22" t="n">
-        <v>-655</v>
-      </c>
-      <c r="F111" s="22" t="n">
-        <v>-404</v>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>788</v>
-      </c>
-      <c r="H111" s="22" t="n">
-        <v>-1422</v>
-      </c>
-      <c r="I111" s="22" t="n">
-        <v>1221</v>
-      </c>
-      <c r="J111" s="22" t="n">
-        <v>162</v>
-      </c>
-      <c r="K111" s="22" t="n">
-        <v>-881</v>
-      </c>
-      <c r="L111" s="22" t="n">
-        <v>-502</v>
-      </c>
-      <c r="M111" s="22" t="n">
-        <v>245</v>
-      </c>
-      <c r="N111" s="22" t="n">
-        <v>697</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>-257</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>-655</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>1221</v>
-      </c>
-      <c r="X111" s="22" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C112" s="12" t="n">
-        <v>1122</v>
-      </c>
-      <c r="D112" s="12" t="n">
-        <v>1509</v>
-      </c>
-      <c r="E112" s="12" t="n">
-        <v>206</v>
-      </c>
-      <c r="F112" s="12" t="n">
-        <v>413</v>
-      </c>
-      <c r="G112" s="12" t="n">
-        <v>1873</v>
-      </c>
-      <c r="H112" s="12" t="n">
-        <v>-236</v>
-      </c>
-      <c r="I112" s="12" t="n">
-        <v>2522</v>
-      </c>
-      <c r="J112" s="12" t="n">
-        <v>1730</v>
-      </c>
-      <c r="K112" s="12" t="n">
-        <v>854</v>
-      </c>
-      <c r="L112" s="12" t="n">
-        <v>1199</v>
-      </c>
-      <c r="M112" s="12" t="n">
-        <v>1292</v>
-      </c>
-      <c r="N112" s="12" t="n">
-        <v>3238</v>
-      </c>
-      <c r="U112" s="12" t="n">
-        <v>1166</v>
-      </c>
-      <c r="V112" s="12" t="n">
-        <v>206</v>
-      </c>
-      <c r="W112" s="12" t="n">
-        <v>2522</v>
-      </c>
-      <c r="X112" s="12" t="n">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="n">
-        <v>1122</v>
-      </c>
-      <c r="D113" s="12" t="n">
-        <v>1509</v>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v>206</v>
-      </c>
-      <c r="F113" s="12" t="n">
-        <v>413</v>
-      </c>
-      <c r="G113" s="12" t="n">
-        <v>1873</v>
-      </c>
-      <c r="H113" s="12" t="n">
-        <v>-236</v>
-      </c>
-      <c r="I113" s="12" t="n">
-        <v>2522</v>
-      </c>
-      <c r="J113" s="12" t="n">
-        <v>1730</v>
-      </c>
-      <c r="K113" s="12" t="n">
-        <v>854</v>
-      </c>
-      <c r="L113" s="12" t="n">
-        <v>1199</v>
-      </c>
-      <c r="M113" s="12" t="n">
-        <v>1292</v>
-      </c>
-      <c r="N113" s="12" t="n">
-        <v>3238</v>
-      </c>
-      <c r="U113" s="12" t="n">
-        <v>1166</v>
-      </c>
-      <c r="V113" s="12" t="n">
-        <v>206</v>
-      </c>
-      <c r="W113" s="12" t="n">
-        <v>2522</v>
-      </c>
-      <c r="X113" s="12" t="n">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="18" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B115" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C115" s="18" t="n"/>
-      <c r="D115" s="18" t="n"/>
-      <c r="E115" s="18" t="n"/>
-      <c r="F115" s="18" t="n"/>
-      <c r="G115" s="18" t="n"/>
-      <c r="H115" s="18" t="n"/>
-      <c r="I115" s="18" t="n"/>
-      <c r="J115" s="18" t="n"/>
-      <c r="K115" s="18" t="n"/>
-      <c r="L115" s="18" t="n"/>
-      <c r="M115" s="18" t="n"/>
-      <c r="N115" s="18" t="n"/>
-      <c r="O115" s="18" t="n"/>
-      <c r="P115" s="18" t="n"/>
-      <c r="Q115" s="18" t="n"/>
-      <c r="R115" s="18" t="n"/>
-      <c r="S115" s="18" t="n"/>
-      <c r="T115" s="18" t="n"/>
-      <c r="U115" s="18" t="n"/>
-      <c r="V115" s="18" t="n"/>
-      <c r="W115" s="18" t="n"/>
-      <c r="X115" s="18" t="n"/>
-      <c r="Y115" s="18" t="n"/>
-      <c r="Z115" s="18" t="n"/>
-      <c r="AA115" s="18" t="n"/>
-      <c r="AB115" s="18" t="n"/>
-      <c r="AC115" s="18" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I116" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J116" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K116" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L116" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M116" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N116" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O116" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P116" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q116" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R116" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S116" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T116" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U116" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V116" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W116" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X116" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y116" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z116" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA116" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB116" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC116" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="n">
-        <v>2448</v>
-      </c>
-      <c r="E117" s="12" t="n">
-        <v>4909</v>
-      </c>
-      <c r="G117" s="12" t="n">
-        <v>2748</v>
-      </c>
-      <c r="I117" s="12" t="n">
-        <v>6065</v>
-      </c>
-      <c r="K117" s="12" t="n">
-        <v>4880</v>
-      </c>
-      <c r="M117" s="12" t="n">
-        <v>8652</v>
-      </c>
-      <c r="T117" s="12" t="n">
-        <v>10627</v>
-      </c>
-      <c r="U117" s="12" t="n">
-        <v>3516</v>
-      </c>
-      <c r="V117" s="12" t="n">
-        <v>4909</v>
-      </c>
-      <c r="W117" s="12" t="n">
-        <v>6065</v>
-      </c>
-      <c r="X117" s="12" t="n">
-        <v>8652</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>기타포괄손익 합계</t>
         </is>
       </c>
       <c r="C118" s="22" t="n">
-        <v>338</v>
+        <v>145</v>
+      </c>
+      <c r="D118" s="22" t="n">
+        <v>651</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>676</v>
+        <v>-655</v>
+      </c>
+      <c r="F118" s="22" t="n">
+        <v>-404</v>
       </c>
       <c r="G118" s="22" t="n">
-        <v>337</v>
+        <v>788</v>
+      </c>
+      <c r="H118" s="22" t="n">
+        <v>-1422</v>
       </c>
       <c r="I118" s="22" t="n">
-        <v>675</v>
+        <v>1221</v>
+      </c>
+      <c r="J118" s="22" t="n">
+        <v>162</v>
       </c>
       <c r="K118" s="22" t="n">
-        <v>339</v>
+        <v>-881</v>
+      </c>
+      <c r="L118" s="22" t="n">
+        <v>-502</v>
       </c>
       <c r="M118" s="22" t="n">
-        <v>679</v>
-      </c>
-      <c r="T118" s="22" t="n">
-        <v>170</v>
+        <v>245</v>
+      </c>
+      <c r="N118" s="22" t="n">
+        <v>697</v>
       </c>
       <c r="U118" s="22" t="n">
-        <v>459</v>
+        <v>-257</v>
       </c>
       <c r="V118" s="22" t="n">
-        <v>676</v>
+        <v>-655</v>
       </c>
       <c r="W118" s="22" t="n">
-        <v>675</v>
+        <v>1221</v>
       </c>
       <c r="X118" s="22" t="n">
-        <v>679</v>
+        <v>245</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="C119" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="E119" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="G119" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="I119" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="K119" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="M119" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="T119" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="U119" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="V119" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="W119" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="X119" s="22" t="n">
-        <v>52</v>
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="n">
+        <v>1122</v>
+      </c>
+      <c r="D119" s="12" t="n">
+        <v>1509</v>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>413</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>1873</v>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>-236</v>
+      </c>
+      <c r="I119" s="12" t="n">
+        <v>2522</v>
+      </c>
+      <c r="J119" s="12" t="n">
+        <v>1730</v>
+      </c>
+      <c r="K119" s="12" t="n">
+        <v>854</v>
+      </c>
+      <c r="L119" s="12" t="n">
+        <v>1199</v>
+      </c>
+      <c r="M119" s="12" t="n">
+        <v>1292</v>
+      </c>
+      <c r="N119" s="12" t="n">
+        <v>3238</v>
+      </c>
+      <c r="U119" s="12" t="n">
+        <v>1166</v>
+      </c>
+      <c r="V119" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="W119" s="12" t="n">
+        <v>2522</v>
+      </c>
+      <c r="X119" s="12" t="n">
+        <v>1292</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="T120" s="22" t="n">
-        <v>-37</v>
-      </c>
-      <c r="U120" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="20" t="inlineStr">
-        <is>
-          <t>이자수익</t>
-        </is>
-      </c>
-      <c r="T121" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="U121" s="22" t="n">
-        <v>-0</v>
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="n">
+        <v>1122</v>
+      </c>
+      <c r="D120" s="12" t="n">
+        <v>1509</v>
+      </c>
+      <c r="E120" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>413</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>1873</v>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>-236</v>
+      </c>
+      <c r="I120" s="12" t="n">
+        <v>2522</v>
+      </c>
+      <c r="J120" s="12" t="n">
+        <v>1730</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>854</v>
+      </c>
+      <c r="L120" s="12" t="n">
+        <v>1199</v>
+      </c>
+      <c r="M120" s="12" t="n">
+        <v>1292</v>
+      </c>
+      <c r="N120" s="12" t="n">
+        <v>3238</v>
+      </c>
+      <c r="U120" s="12" t="n">
+        <v>1166</v>
+      </c>
+      <c r="V120" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="W120" s="12" t="n">
+        <v>2522</v>
+      </c>
+      <c r="X120" s="12" t="n">
+        <v>1292</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C122" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="22" t="n">
-        <v>136</v>
-      </c>
-      <c r="G122" s="22" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I122" s="22" t="n">
-        <v>38</v>
-      </c>
-      <c r="K122" s="22" t="n">
-        <v>-75</v>
-      </c>
-      <c r="M122" s="22" t="n">
-        <v>59</v>
-      </c>
-      <c r="U122" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" s="22" t="n">
-        <v>136</v>
-      </c>
-      <c r="W122" s="22" t="n">
-        <v>38</v>
-      </c>
-      <c r="X122" s="22" t="n">
-        <v>59</v>
-      </c>
+      <c r="A122" s="18" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B122" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="n"/>
+      <c r="D122" s="18" t="n"/>
+      <c r="E122" s="18" t="n"/>
+      <c r="F122" s="18" t="n"/>
+      <c r="G122" s="18" t="n"/>
+      <c r="H122" s="18" t="n"/>
+      <c r="I122" s="18" t="n"/>
+      <c r="J122" s="18" t="n"/>
+      <c r="K122" s="18" t="n"/>
+      <c r="L122" s="18" t="n"/>
+      <c r="M122" s="18" t="n"/>
+      <c r="N122" s="18" t="n"/>
+      <c r="O122" s="18" t="n"/>
+      <c r="P122" s="18" t="n"/>
+      <c r="Q122" s="18" t="n"/>
+      <c r="R122" s="18" t="n"/>
+      <c r="S122" s="18" t="n"/>
+      <c r="T122" s="18" t="n"/>
+      <c r="U122" s="18" t="n"/>
+      <c r="V122" s="18" t="n"/>
+      <c r="W122" s="18" t="n"/>
+      <c r="X122" s="18" t="n"/>
+      <c r="Y122" s="18" t="n"/>
+      <c r="Z122" s="18" t="n"/>
+      <c r="AA122" s="18" t="n"/>
+      <c r="AB122" s="18" t="n"/>
+      <c r="AC122" s="18" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="20" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="C123" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E123" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G123" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I123" s="22" t="n">
-        <v>-7</v>
-      </c>
-      <c r="K123" s="22" t="n">
-        <v>-14</v>
-      </c>
-      <c r="M123" s="22" t="n">
-        <v>-32</v>
-      </c>
-      <c r="U123" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="V123" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W123" s="22" t="n">
-        <v>-7</v>
-      </c>
-      <c r="X123" s="22" t="n">
-        <v>-32</v>
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N123" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O123" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P123" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q123" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R123" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S123" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T123" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U123" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V123" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W123" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X123" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y123" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z123" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA123" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB123" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC123" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="C124" s="22" t="n">
-        <v>201</v>
-      </c>
-      <c r="E124" s="22" t="n">
-        <v>483</v>
-      </c>
-      <c r="G124" s="22" t="n">
-        <v>353</v>
-      </c>
-      <c r="I124" s="22" t="n">
-        <v>877</v>
-      </c>
-      <c r="K124" s="22" t="n">
-        <v>598</v>
-      </c>
-      <c r="M124" s="22" t="n">
-        <v>1230</v>
-      </c>
-      <c r="T124" s="22" t="n">
-        <v>625</v>
-      </c>
-      <c r="U124" s="22" t="n">
-        <v>384</v>
-      </c>
-      <c r="V124" s="22" t="n">
-        <v>483</v>
-      </c>
-      <c r="W124" s="22" t="n">
-        <v>877</v>
-      </c>
-      <c r="X124" s="22" t="n">
-        <v>1230</v>
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="n">
+        <v>2448</v>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>4909</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>2748</v>
+      </c>
+      <c r="I124" s="12" t="n">
+        <v>6065</v>
+      </c>
+      <c r="K124" s="12" t="n">
+        <v>4880</v>
+      </c>
+      <c r="M124" s="12" t="n">
+        <v>8652</v>
+      </c>
+      <c r="T124" s="12" t="n">
+        <v>10627</v>
+      </c>
+      <c r="U124" s="12" t="n">
+        <v>3516</v>
+      </c>
+      <c r="V124" s="12" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W124" s="12" t="n">
+        <v>6065</v>
+      </c>
+      <c r="X124" s="12" t="n">
+        <v>8652</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각손익</t>
-        </is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C125" s="22" t="n">
+        <v>338</v>
+      </c>
+      <c r="E125" s="22" t="n">
+        <v>676</v>
+      </c>
+      <c r="G125" s="22" t="n">
+        <v>337</v>
+      </c>
+      <c r="I125" s="22" t="n">
+        <v>675</v>
+      </c>
+      <c r="K125" s="22" t="n">
+        <v>339</v>
+      </c>
+      <c r="M125" s="22" t="n">
+        <v>679</v>
       </c>
       <c r="T125" s="22" t="n">
-        <v>-7820</v>
+        <v>170</v>
       </c>
       <c r="U125" s="22" t="n">
-        <v>0</v>
+        <v>459</v>
+      </c>
+      <c r="V125" s="22" t="n">
+        <v>676</v>
+      </c>
+      <c r="W125" s="22" t="n">
+        <v>675</v>
+      </c>
+      <c r="X125" s="22" t="n">
+        <v>679</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
+          <t>영업권 상각</t>
+        </is>
+      </c>
+      <c r="C126" s="22" t="n">
+        <v>26</v>
       </c>
       <c r="E126" s="22" t="n">
-        <v>17</v>
+        <v>52</v>
+      </c>
+      <c r="G126" s="22" t="n">
+        <v>26</v>
       </c>
       <c r="I126" s="22" t="n">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="K126" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="M126" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="T126" s="22" t="n">
+        <v>52</v>
       </c>
       <c r="U126" s="22" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="V126" s="22" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="W126" s="22" t="n">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="X126" s="22" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Operating Receivables Ope CF</t>
-        </is>
-      </c>
-      <c r="C127" s="22" t="n">
-        <v>-213</v>
-      </c>
-      <c r="E127" s="22" t="n">
-        <v>150</v>
-      </c>
-      <c r="G127" s="22" t="n">
-        <v>-117</v>
-      </c>
-      <c r="I127" s="22" t="n">
-        <v>-746</v>
-      </c>
-      <c r="K127" s="22" t="n">
-        <v>-78</v>
-      </c>
-      <c r="M127" s="22" t="n">
-        <v>238</v>
+          <t>대손충당금 증감</t>
+        </is>
       </c>
       <c r="T127" s="22" t="n">
-        <v>-308</v>
+        <v>-37</v>
       </c>
       <c r="U127" s="22" t="n">
-        <v>373</v>
-      </c>
-      <c r="V127" s="22" t="n">
-        <v>150</v>
-      </c>
-      <c r="W127" s="22" t="n">
-        <v>-746</v>
-      </c>
-      <c r="X127" s="22" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>선급금 증감</t>
-        </is>
-      </c>
-      <c r="E128" s="22" t="n">
-        <v>556</v>
-      </c>
-      <c r="G128" s="22" t="n">
-        <v>-1304</v>
-      </c>
-      <c r="I128" s="22" t="n">
-        <v>-5834</v>
-      </c>
-      <c r="K128" s="22" t="n">
-        <v>5922</v>
-      </c>
-      <c r="M128" s="22" t="n">
-        <v>5965</v>
-      </c>
-      <c r="V128" s="22" t="n">
-        <v>556</v>
-      </c>
-      <c r="W128" s="22" t="n">
-        <v>-5834</v>
-      </c>
-      <c r="X128" s="22" t="n">
-        <v>5965</v>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="T128" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U128" s="22" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="C129" s="22" t="n">
-        <v>-10913</v>
+        <v>0</v>
       </c>
       <c r="E129" s="22" t="n">
-        <v>-29217</v>
+        <v>136</v>
       </c>
       <c r="G129" s="22" t="n">
-        <v>-3993</v>
+        <v>-60</v>
       </c>
       <c r="I129" s="22" t="n">
-        <v>-26280</v>
+        <v>38</v>
       </c>
       <c r="K129" s="22" t="n">
-        <v>1725</v>
+        <v>-75</v>
       </c>
       <c r="M129" s="22" t="n">
-        <v>-14246</v>
-      </c>
-      <c r="T129" s="22" t="n">
-        <v>-4182</v>
+        <v>59</v>
       </c>
       <c r="U129" s="22" t="n">
-        <v>-3466</v>
+        <v>0</v>
       </c>
       <c r="V129" s="22" t="n">
-        <v>-29217</v>
+        <v>136</v>
       </c>
       <c r="W129" s="22" t="n">
-        <v>-26280</v>
+        <v>38</v>
       </c>
       <c r="X129" s="22" t="n">
-        <v>-14246</v>
+        <v>59</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="C130" s="22" t="n">
-        <v>-600</v>
-      </c>
-      <c r="T130" s="22" t="n">
-        <v>285</v>
+        <v>-0</v>
+      </c>
+      <c r="E130" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G130" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I130" s="22" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K130" s="22" t="n">
+        <v>-14</v>
+      </c>
+      <c r="M130" s="22" t="n">
+        <v>-32</v>
       </c>
       <c r="U130" s="22" t="n">
-        <v>2560</v>
+        <v>-0</v>
+      </c>
+      <c r="V130" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W130" s="22" t="n">
+        <v>-7</v>
+      </c>
+      <c r="X130" s="22" t="n">
+        <v>-32</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C131" s="22" t="n">
-        <v>-600</v>
+        <v>201</v>
       </c>
       <c r="E131" s="22" t="n">
-        <v>198</v>
+        <v>483</v>
       </c>
       <c r="G131" s="22" t="n">
-        <v>-607</v>
+        <v>353</v>
       </c>
       <c r="I131" s="22" t="n">
-        <v>1441</v>
+        <v>877</v>
       </c>
       <c r="K131" s="22" t="n">
-        <v>-667</v>
+        <v>598</v>
       </c>
       <c r="M131" s="22" t="n">
-        <v>1633</v>
+        <v>1230</v>
+      </c>
+      <c r="T131" s="22" t="n">
+        <v>625</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>2560</v>
+        <v>384</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>198</v>
+        <v>483</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>1441</v>
+        <v>877</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>1633</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C132" s="22" t="n">
-        <v>-443</v>
-      </c>
-      <c r="E132" s="22" t="n">
-        <v>-961</v>
-      </c>
-      <c r="G132" s="22" t="n">
-        <v>797</v>
-      </c>
-      <c r="I132" s="22" t="n">
-        <v>266</v>
-      </c>
-      <c r="K132" s="22" t="n">
-        <v>55</v>
-      </c>
-      <c r="M132" s="22" t="n">
-        <v>137</v>
+          <t>유형자산 매각손익</t>
+        </is>
       </c>
       <c r="T132" s="22" t="n">
-        <v>293</v>
+        <v>-7820</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>142</v>
-      </c>
-      <c r="V132" s="22" t="n">
-        <v>-961</v>
-      </c>
-      <c r="W132" s="22" t="n">
-        <v>266</v>
-      </c>
-      <c r="X132" s="22" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
-        </is>
-      </c>
-      <c r="C133" s="22" t="n">
-        <v>-9156</v>
+          <t>고정자산 제각손실</t>
+        </is>
       </c>
       <c r="E133" s="22" t="n">
-        <v>-22998</v>
-      </c>
-      <c r="G133" s="22" t="n">
-        <v>-1821</v>
+        <v>17</v>
       </c>
       <c r="I133" s="22" t="n">
-        <v>-23452</v>
-      </c>
-      <c r="K133" s="22" t="n">
-        <v>12712</v>
-      </c>
-      <c r="M133" s="22" t="n">
-        <v>4368</v>
-      </c>
-      <c r="T133" s="22" t="n">
-        <v>-295</v>
+        <v>0</v>
       </c>
       <c r="U133" s="22" t="n">
-        <v>4022</v>
+        <v>0</v>
       </c>
       <c r="V133" s="22" t="n">
-        <v>-22998</v>
+        <v>17</v>
       </c>
       <c r="W133" s="22" t="n">
-        <v>-23452</v>
-      </c>
-      <c r="X133" s="22" t="n">
-        <v>4368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>이자 수취</t>
-        </is>
+          <t>Decrease Increase In Operating Receivables Ope CF</t>
+        </is>
+      </c>
+      <c r="C134" s="22" t="n">
+        <v>-213</v>
+      </c>
+      <c r="E134" s="22" t="n">
+        <v>150</v>
+      </c>
+      <c r="G134" s="22" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I134" s="22" t="n">
+        <v>-746</v>
+      </c>
+      <c r="K134" s="22" t="n">
+        <v>-78</v>
+      </c>
+      <c r="M134" s="22" t="n">
+        <v>238</v>
       </c>
       <c r="T134" s="22" t="n">
-        <v>0</v>
+        <v>-308</v>
       </c>
       <c r="U134" s="22" t="n">
-        <v>0</v>
+        <v>373</v>
+      </c>
+      <c r="V134" s="22" t="n">
+        <v>150</v>
+      </c>
+      <c r="W134" s="22" t="n">
+        <v>-746</v>
+      </c>
+      <c r="X134" s="22" t="n">
+        <v>238</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
-        </is>
-      </c>
-      <c r="C135" s="22" t="n">
-        <v>0</v>
+          <t>선급금 증감</t>
+        </is>
       </c>
       <c r="E135" s="22" t="n">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>1</v>
+        <v>-1304</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>7</v>
+        <v>-5834</v>
       </c>
       <c r="K135" s="22" t="n">
-        <v>14</v>
+        <v>5922</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>32</v>
-      </c>
-      <c r="U135" s="22" t="n">
-        <v>0</v>
+        <v>5965</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>7</v>
+        <v>-5834</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>32</v>
+        <v>5965</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="C136" s="22" t="n">
-        <v>-167</v>
+        <v>-10913</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>-443</v>
+        <v>-29217</v>
       </c>
       <c r="G136" s="22" t="n">
-        <v>-318</v>
+        <v>-3993</v>
       </c>
       <c r="I136" s="22" t="n">
-        <v>-866</v>
+        <v>-26280</v>
       </c>
       <c r="K136" s="22" t="n">
-        <v>-585</v>
+        <v>1725</v>
       </c>
       <c r="M136" s="22" t="n">
-        <v>-1223</v>
+        <v>-14246</v>
       </c>
       <c r="T136" s="22" t="n">
-        <v>-730</v>
+        <v>-4182</v>
       </c>
       <c r="U136" s="22" t="n">
-        <v>-306</v>
+        <v>-3466</v>
       </c>
       <c r="V136" s="22" t="n">
-        <v>-443</v>
+        <v>-29217</v>
       </c>
       <c r="W136" s="22" t="n">
-        <v>-866</v>
+        <v>-26280</v>
       </c>
       <c r="X136" s="22" t="n">
-        <v>-1223</v>
+        <v>-14246</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="C137" s="22" t="n">
-        <v>-2693</v>
-      </c>
-      <c r="E137" s="22" t="n">
-        <v>-3209</v>
-      </c>
-      <c r="G137" s="22" t="n">
-        <v>-1292</v>
-      </c>
-      <c r="I137" s="22" t="n">
-        <v>-2198</v>
-      </c>
-      <c r="K137" s="22" t="n">
-        <v>-1806</v>
-      </c>
-      <c r="M137" s="22" t="n">
-        <v>-3164</v>
+        <v>-600</v>
       </c>
       <c r="T137" s="22" t="n">
-        <v>-3</v>
+        <v>285</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="V137" s="22" t="n">
-        <v>-3209</v>
-      </c>
-      <c r="W137" s="22" t="n">
-        <v>-2198</v>
-      </c>
-      <c r="X137" s="22" t="n">
-        <v>-3164</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="C138" s="22" t="n">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>2</v>
+        <v>-607</v>
       </c>
       <c r="I138" s="22" t="n">
-        <v>3</v>
+        <v>1441</v>
       </c>
       <c r="K138" s="22" t="n">
-        <v>0</v>
+        <v>-667</v>
       </c>
       <c r="M138" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" s="22" t="n">
-        <v>256</v>
+        <v>1633</v>
       </c>
       <c r="U138" s="22" t="n">
-        <v>0</v>
+        <v>2560</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>3</v>
+        <v>1441</v>
       </c>
       <c r="X138" s="22" t="n">
-        <v>0</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C139" s="12" t="n">
-        <v>-12017</v>
-      </c>
-      <c r="E139" s="12" t="n">
-        <v>-26652</v>
-      </c>
-      <c r="G139" s="12" t="n">
-        <v>-3429</v>
-      </c>
-      <c r="I139" s="12" t="n">
-        <v>-26506</v>
-      </c>
-      <c r="K139" s="12" t="n">
-        <v>10334</v>
-      </c>
-      <c r="M139" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="T139" s="12" t="n">
-        <v>-772</v>
-      </c>
-      <c r="U139" s="12" t="n">
-        <v>3711</v>
-      </c>
-      <c r="V139" s="12" t="n">
-        <v>-26652</v>
-      </c>
-      <c r="W139" s="12" t="n">
-        <v>-26506</v>
-      </c>
-      <c r="X139" s="12" t="n">
-        <v>13</v>
+      <c r="A139" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C139" s="22" t="n">
+        <v>-443</v>
+      </c>
+      <c r="E139" s="22" t="n">
+        <v>-961</v>
+      </c>
+      <c r="G139" s="22" t="n">
+        <v>797</v>
+      </c>
+      <c r="I139" s="22" t="n">
+        <v>266</v>
+      </c>
+      <c r="K139" s="22" t="n">
+        <v>55</v>
+      </c>
+      <c r="M139" s="22" t="n">
+        <v>137</v>
+      </c>
+      <c r="T139" s="22" t="n">
+        <v>293</v>
+      </c>
+      <c r="U139" s="22" t="n">
+        <v>142</v>
+      </c>
+      <c r="V139" s="22" t="n">
+        <v>-961</v>
+      </c>
+      <c r="W139" s="22" t="n">
+        <v>266</v>
+      </c>
+      <c r="X139" s="22" t="n">
+        <v>137</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="C140" s="22" t="n">
-        <v>-3</v>
+        <v>-9156</v>
       </c>
       <c r="E140" s="22" t="n">
-        <v>-3</v>
+        <v>-22998</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>-3</v>
+        <v>-1821</v>
       </c>
       <c r="I140" s="22" t="n">
-        <v>-3</v>
+        <v>-23452</v>
       </c>
       <c r="K140" s="22" t="n">
-        <v>-14</v>
+        <v>12712</v>
       </c>
       <c r="M140" s="22" t="n">
-        <v>-17</v>
+        <v>4368</v>
       </c>
       <c r="T140" s="22" t="n">
-        <v>-42</v>
+        <v>-295</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>-8228</v>
+        <v>4022</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>-3</v>
+        <v>-22998</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>-3</v>
+        <v>-23452</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>-17</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
-        </is>
-      </c>
-      <c r="E141" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I141" s="22" t="n">
+          <t>이자 수취</t>
+        </is>
+      </c>
+      <c r="T141" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="T141" s="22" t="n">
-        <v>26214</v>
       </c>
       <c r="U141" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="W141" s="22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="C142" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="G142" s="22" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>-25</v>
+        <v>7</v>
       </c>
       <c r="K142" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="M142" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="U142" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M142" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T142" s="22" t="n">
+      <c r="V142" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U142" s="22" t="n">
-        <v>-25</v>
-      </c>
-      <c r="V142" s="22" t="n">
-        <v>-34</v>
-      </c>
       <c r="W142" s="22" t="n">
-        <v>-25</v>
+        <v>7</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>-1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>관계회사 주식 취득</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="C143" s="22" t="n">
-        <v>-53</v>
+        <v>-167</v>
       </c>
       <c r="E143" s="22" t="n">
-        <v>-114</v>
+        <v>-443</v>
       </c>
       <c r="G143" s="22" t="n">
-        <v>-28</v>
+        <v>-318</v>
       </c>
       <c r="I143" s="22" t="n">
-        <v>-60</v>
+        <v>-866</v>
       </c>
       <c r="K143" s="22" t="n">
-        <v>-76</v>
+        <v>-585</v>
       </c>
       <c r="M143" s="22" t="n">
-        <v>-215</v>
+        <v>-1223</v>
       </c>
       <c r="T143" s="22" t="n">
-        <v>-72</v>
+        <v>-730</v>
       </c>
       <c r="U143" s="22" t="n">
-        <v>-84</v>
+        <v>-306</v>
       </c>
       <c r="V143" s="22" t="n">
-        <v>-114</v>
+        <v>-443</v>
       </c>
       <c r="W143" s="22" t="n">
-        <v>-60</v>
+        <v>-866</v>
       </c>
       <c r="X143" s="22" t="n">
-        <v>-215</v>
+        <v>-1223</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>관계회사 출자금 납입</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="C144" s="22" t="n">
-        <v>-8</v>
+        <v>-2693</v>
       </c>
       <c r="E144" s="22" t="n">
-        <v>-38</v>
+        <v>-3209</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>-10</v>
+        <v>-1292</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>-34</v>
+        <v>-2198</v>
       </c>
       <c r="K144" s="22" t="n">
-        <v>-4</v>
+        <v>-1806</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>-20</v>
+        <v>-3164</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>-29</v>
+        <v>-5</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>-38</v>
+        <v>-3209</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>-34</v>
+        <v>-2198</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>-20</v>
+        <v>-3164</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>법인세 환급</t>
         </is>
       </c>
       <c r="C145" s="22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E145" s="22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>-0</v>
+        <v>3</v>
       </c>
       <c r="K145" s="22" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="M145" s="22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T145" s="22" t="n">
-        <v>-10</v>
+        <v>256</v>
       </c>
       <c r="U145" s="22" t="n">
-        <v>-66</v>
+        <v>0</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W145" s="22" t="n">
-        <v>-0</v>
+        <v>3</v>
       </c>
       <c r="X145" s="22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>투자활동 현금흐름</t>
+          <t>영업활동 현금흐름</t>
         </is>
       </c>
       <c r="C146" s="12" t="n">
-        <v>-66</v>
+        <v>-12017</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>-189</v>
+        <v>-26652</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>-50</v>
+        <v>-3429</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-123</v>
+        <v>-26506</v>
       </c>
       <c r="K146" s="12" t="n">
-        <v>-105</v>
+        <v>10334</v>
       </c>
       <c r="M146" s="12" t="n">
-        <v>-254</v>
+        <v>13</v>
       </c>
       <c r="T146" s="12" t="n">
-        <v>26082</v>
+        <v>-772</v>
       </c>
       <c r="U146" s="12" t="n">
-        <v>-8434</v>
+        <v>3711</v>
       </c>
       <c r="V146" s="12" t="n">
-        <v>-189</v>
+        <v>-26652</v>
       </c>
       <c r="W146" s="12" t="n">
-        <v>-123</v>
+        <v>-26506</v>
       </c>
       <c r="X146" s="12" t="n">
-        <v>-254</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 순증감</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="C147" s="22" t="n">
-        <v>10200</v>
+        <v>-3</v>
       </c>
       <c r="E147" s="22" t="n">
-        <v>24199</v>
+        <v>-3</v>
       </c>
       <c r="G147" s="22" t="n">
-        <v>7900</v>
+        <v>-3</v>
       </c>
       <c r="I147" s="22" t="n">
-        <v>18000</v>
+        <v>-3</v>
       </c>
       <c r="K147" s="22" t="n">
-        <v>-8442</v>
+        <v>-14</v>
       </c>
       <c r="M147" s="22" t="n">
-        <v>-7500</v>
+        <v>-17</v>
       </c>
       <c r="T147" s="22" t="n">
-        <v>-3690</v>
+        <v>-42</v>
       </c>
       <c r="U147" s="22" t="n">
-        <v>-6319</v>
+        <v>-8228</v>
       </c>
       <c r="V147" s="22" t="n">
-        <v>24199</v>
+        <v>-3</v>
       </c>
       <c r="W147" s="22" t="n">
-        <v>18000</v>
+        <v>-3</v>
       </c>
       <c r="X147" s="22" t="n">
-        <v>-7500</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>기업어음(CP) 순증감액</t>
-        </is>
-      </c>
-      <c r="C148" s="22" t="n">
+          <t>유형자산 매각</t>
+        </is>
+      </c>
+      <c r="E148" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I148" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E148" s="22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G148" s="22" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I148" s="22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K148" s="22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M148" s="22" t="n">
-        <v>0</v>
+      <c r="T148" s="22" t="n">
+        <v>26214</v>
       </c>
       <c r="U148" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X148" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="C149" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E149" s="22" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G149" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I149" s="22" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K149" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G149" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" s="22" t="n">
-        <v>1000</v>
-      </c>
       <c r="M149" s="22" t="n">
-        <v>10100</v>
+        <v>-1</v>
       </c>
       <c r="T149" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>14658</v>
+        <v>-25</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="X149" s="22" t="n">
-        <v>10100</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
+          <t>관계회사 주식 취득</t>
         </is>
       </c>
       <c r="C150" s="22" t="n">
-        <v>-251</v>
+        <v>-53</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-502</v>
+        <v>-114</v>
       </c>
       <c r="G150" s="22" t="n">
-        <v>-251</v>
+        <v>-28</v>
       </c>
       <c r="I150" s="22" t="n">
-        <v>-502</v>
+        <v>-60</v>
       </c>
       <c r="K150" s="22" t="n">
-        <v>-251</v>
+        <v>-76</v>
       </c>
       <c r="M150" s="22" t="n">
-        <v>-8632</v>
+        <v>-215</v>
       </c>
       <c r="T150" s="22" t="n">
-        <v>0</v>
+        <v>-72</v>
       </c>
       <c r="U150" s="22" t="n">
-        <v>-251</v>
+        <v>-84</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>-502</v>
+        <v>-114</v>
       </c>
       <c r="W150" s="22" t="n">
-        <v>-502</v>
+        <v>-60</v>
       </c>
       <c r="X150" s="22" t="n">
-        <v>-8632</v>
+        <v>-215</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>Repayments Of Long Term Non Recourse Loans Fin CF</t>
-        </is>
+          <t>관계회사 출자금 납입</t>
+        </is>
+      </c>
+      <c r="C151" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E151" s="22" t="n">
+        <v>-38</v>
+      </c>
+      <c r="G151" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I151" s="22" t="n">
+        <v>-34</v>
+      </c>
+      <c r="K151" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M151" s="22" t="n">
+        <v>-20</v>
       </c>
       <c r="T151" s="22" t="n">
-        <v>-18525</v>
+        <v>-6</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>0</v>
+        <v>-29</v>
+      </c>
+      <c r="V151" s="22" t="n">
+        <v>-38</v>
+      </c>
+      <c r="W151" s="22" t="n">
+        <v>-34</v>
+      </c>
+      <c r="X151" s="22" t="n">
+        <v>-20</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C152" s="22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E152" s="22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G152" s="22" t="n">
-        <v>59</v>
+        <v>-0</v>
+      </c>
+      <c r="I152" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K152" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="M152" s="22" t="n">
+        <v>-0</v>
       </c>
       <c r="T152" s="22" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="U152" s="22" t="n">
-        <v>1851</v>
+        <v>-66</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="W152" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X152" s="22" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="20" t="inlineStr">
-        <is>
-          <t>사채 발행</t>
-        </is>
-      </c>
-      <c r="E153" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" s="22" t="n">
-        <v>4973</v>
-      </c>
-      <c r="M153" s="22" t="n">
-        <v>5969</v>
-      </c>
-      <c r="V153" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W153" s="22" t="n">
-        <v>4973</v>
-      </c>
-      <c r="X153" s="22" t="n">
-        <v>5969</v>
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="n">
+        <v>-66</v>
+      </c>
+      <c r="E153" s="12" t="n">
+        <v>-189</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I153" s="12" t="n">
+        <v>-123</v>
+      </c>
+      <c r="K153" s="12" t="n">
+        <v>-105</v>
+      </c>
+      <c r="M153" s="12" t="n">
+        <v>-254</v>
+      </c>
+      <c r="T153" s="12" t="n">
+        <v>26082</v>
+      </c>
+      <c r="U153" s="12" t="n">
+        <v>-8434</v>
+      </c>
+      <c r="V153" s="12" t="n">
+        <v>-189</v>
+      </c>
+      <c r="W153" s="12" t="n">
+        <v>-123</v>
+      </c>
+      <c r="X153" s="12" t="n">
+        <v>-254</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 행사에 따른 주식 발행</t>
-        </is>
+          <t>단기차입금 순증감</t>
+        </is>
+      </c>
+      <c r="C154" s="22" t="n">
+        <v>10200</v>
       </c>
       <c r="E154" s="22" t="n">
-        <v>0</v>
+        <v>24199</v>
       </c>
       <c r="G154" s="22" t="n">
-        <v>59</v>
+        <v>7900</v>
       </c>
       <c r="I154" s="22" t="n">
-        <v>229</v>
+        <v>18000</v>
       </c>
       <c r="K154" s="22" t="n">
-        <v>94</v>
+        <v>-8442</v>
       </c>
       <c r="M154" s="22" t="n">
-        <v>190</v>
+        <v>-7500</v>
+      </c>
+      <c r="T154" s="22" t="n">
+        <v>-3690</v>
+      </c>
+      <c r="U154" s="22" t="n">
+        <v>-6319</v>
       </c>
       <c r="V154" s="22" t="n">
-        <v>0</v>
+        <v>24199</v>
       </c>
       <c r="W154" s="22" t="n">
-        <v>229</v>
+        <v>18000</v>
       </c>
       <c r="X154" s="22" t="n">
-        <v>190</v>
+        <v>-7500</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>기업어음(CP) 순증감액</t>
         </is>
       </c>
       <c r="C155" s="22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E155" s="22" t="n">
-        <v>-0</v>
+        <v>2000</v>
       </c>
       <c r="G155" s="22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I155" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K155" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M155" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="I155" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M155" s="22" t="n">
-        <v>-0</v>
       </c>
       <c r="U155" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V155" s="22" t="n">
-        <v>-0</v>
+        <v>2000</v>
       </c>
       <c r="W155" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X155" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="X155" s="22" t="n">
-        <v>-0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 발행</t>
-        </is>
+          <t>장기차입</t>
+        </is>
+      </c>
+      <c r="C156" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="E156" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="G156" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="I156" s="22" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="K156" s="22" t="n">
+        <v>1000</v>
       </c>
       <c r="M156" s="22" t="n">
+        <v>10100</v>
+      </c>
+      <c r="T156" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T156" s="22" t="n">
-        <v>17</v>
-      </c>
       <c r="U156" s="22" t="n">
-        <v>0</v>
+        <v>14658</v>
       </c>
       <c r="V156" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W156" s="22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X156" s="22" t="n">
-        <v>0</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
+          <t>장기차입금 상환</t>
         </is>
       </c>
       <c r="C157" s="22" t="n">
-        <v>-77</v>
+        <v>-251</v>
       </c>
       <c r="E157" s="22" t="n">
-        <v>-77</v>
+        <v>-502</v>
       </c>
       <c r="G157" s="22" t="n">
-        <v>-776</v>
+        <v>-251</v>
       </c>
       <c r="I157" s="22" t="n">
-        <v>-776</v>
+        <v>-502</v>
       </c>
       <c r="K157" s="22" t="n">
-        <v>-1337</v>
+        <v>-251</v>
       </c>
       <c r="M157" s="22" t="n">
-        <v>-1733</v>
+        <v>-8632</v>
+      </c>
+      <c r="T157" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="U157" s="22" t="n">
+        <v>-251</v>
+      </c>
+      <c r="V157" s="22" t="n">
+        <v>-502</v>
+      </c>
+      <c r="W157" s="22" t="n">
+        <v>-502</v>
+      </c>
+      <c r="X157" s="22" t="n">
+        <v>-8632</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="20" t="inlineStr">
+        <is>
+          <t>Repayments Of Long Term Non Recourse Loans Fin CF</t>
+        </is>
+      </c>
+      <c r="T158" s="22" t="n">
+        <v>-18525</v>
+      </c>
+      <c r="U158" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="V157" s="22" t="n">
-        <v>-77</v>
-      </c>
-      <c r="W157" s="22" t="n">
-        <v>-776</v>
-      </c>
-      <c r="X157" s="22" t="n">
-        <v>-1733</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C158" s="12" t="n">
-        <v>9871</v>
-      </c>
-      <c r="E158" s="12" t="n">
-        <v>25619</v>
-      </c>
-      <c r="G158" s="12" t="n">
-        <v>9932</v>
-      </c>
-      <c r="I158" s="12" t="n">
-        <v>22931</v>
-      </c>
-      <c r="K158" s="12" t="n">
-        <v>-6936</v>
-      </c>
-      <c r="M158" s="12" t="n">
-        <v>-1605</v>
-      </c>
-      <c r="T158" s="12" t="n">
-        <v>-22198</v>
-      </c>
-      <c r="U158" s="12" t="n">
-        <v>9939</v>
-      </c>
-      <c r="V158" s="12" t="n">
-        <v>25619</v>
-      </c>
-      <c r="W158" s="12" t="n">
-        <v>22931</v>
-      </c>
-      <c r="X158" s="12" t="n">
-        <v>-1605</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>주식 발행</t>
         </is>
       </c>
       <c r="C159" s="22" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="E159" s="22" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="G159" s="22" t="n">
-        <v>-17</v>
-      </c>
-      <c r="I159" s="22" t="n">
-        <v>-18</v>
-      </c>
-      <c r="K159" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M159" s="22" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="T159" s="22" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="U159" s="22" t="n">
-        <v>-10</v>
+        <v>1851</v>
       </c>
       <c r="V159" s="22" t="n">
-        <v>63</v>
-      </c>
-      <c r="W159" s="22" t="n">
-        <v>-18</v>
-      </c>
-      <c r="X159" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 증감</t>
-        </is>
-      </c>
-      <c r="C160" s="22" t="n">
-        <v>-2147</v>
+          <t>사채 발행</t>
+        </is>
       </c>
       <c r="E160" s="22" t="n">
-        <v>-1158</v>
-      </c>
-      <c r="G160" s="22" t="n">
-        <v>6434</v>
+        <v>0</v>
       </c>
       <c r="I160" s="22" t="n">
-        <v>-3717</v>
-      </c>
-      <c r="K160" s="22" t="n">
-        <v>3293</v>
+        <v>4973</v>
       </c>
       <c r="M160" s="22" t="n">
-        <v>-1841</v>
-      </c>
-      <c r="T160" s="22" t="n">
-        <v>3230</v>
-      </c>
-      <c r="U160" s="22" t="n">
-        <v>5205</v>
+        <v>5969</v>
       </c>
       <c r="V160" s="22" t="n">
-        <v>-1158</v>
+        <v>0</v>
       </c>
       <c r="W160" s="22" t="n">
-        <v>-3717</v>
+        <v>4973</v>
       </c>
       <c r="X160" s="22" t="n">
-        <v>-1841</v>
+        <v>5969</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>신규 연결 현금성자산 증가</t>
-        </is>
-      </c>
-      <c r="C161" s="22" t="n">
-        <v>0</v>
+          <t>신주예약권 행사에 따른 주식 발행</t>
+        </is>
       </c>
       <c r="E161" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T161" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U161" s="22" t="n">
-        <v>1</v>
+      <c r="G161" s="22" t="n">
+        <v>59</v>
+      </c>
+      <c r="I161" s="22" t="n">
+        <v>229</v>
+      </c>
+      <c r="K161" s="22" t="n">
+        <v>94</v>
+      </c>
+      <c r="M161" s="22" t="n">
+        <v>190</v>
       </c>
       <c r="V161" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="W161" s="22" t="n">
+        <v>229</v>
+      </c>
+      <c r="X161" s="22" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="C162" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E162" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G162" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U162" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W162" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" s="22" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="20" t="inlineStr">
+        <is>
+          <t>신주예약권 발행</t>
+        </is>
+      </c>
+      <c r="E163" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M163" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="U163" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="X163" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C164" s="22" t="n">
+        <v>-77</v>
+      </c>
+      <c r="E164" s="22" t="n">
+        <v>-77</v>
+      </c>
+      <c r="G164" s="22" t="n">
+        <v>-776</v>
+      </c>
+      <c r="I164" s="22" t="n">
+        <v>-776</v>
+      </c>
+      <c r="K164" s="22" t="n">
+        <v>-1337</v>
+      </c>
+      <c r="M164" s="22" t="n">
+        <v>-1733</v>
+      </c>
+      <c r="U164" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" s="22" t="n">
+        <v>-77</v>
+      </c>
+      <c r="W164" s="22" t="n">
+        <v>-776</v>
+      </c>
+      <c r="X164" s="22" t="n">
+        <v>-1733</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="n">
+        <v>9871</v>
+      </c>
+      <c r="E165" s="12" t="n">
+        <v>25619</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>9932</v>
+      </c>
+      <c r="I165" s="12" t="n">
+        <v>22931</v>
+      </c>
+      <c r="K165" s="12" t="n">
+        <v>-6936</v>
+      </c>
+      <c r="M165" s="12" t="n">
+        <v>-1605</v>
+      </c>
+      <c r="T165" s="12" t="n">
+        <v>-22198</v>
+      </c>
+      <c r="U165" s="12" t="n">
+        <v>9939</v>
+      </c>
+      <c r="V165" s="12" t="n">
+        <v>25619</v>
+      </c>
+      <c r="W165" s="12" t="n">
+        <v>22931</v>
+      </c>
+      <c r="X165" s="12" t="n">
+        <v>-1605</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="C166" s="22" t="n">
+        <v>65</v>
+      </c>
+      <c r="E166" s="22" t="n">
+        <v>63</v>
+      </c>
+      <c r="G166" s="22" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I166" s="22" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K166" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T166" s="22" t="n">
+        <v>117</v>
+      </c>
+      <c r="U166" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="V166" s="22" t="n">
+        <v>63</v>
+      </c>
+      <c r="W166" s="22" t="n">
+        <v>-18</v>
+      </c>
+      <c r="X166" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 증감</t>
+        </is>
+      </c>
+      <c r="C167" s="22" t="n">
+        <v>-2147</v>
+      </c>
+      <c r="E167" s="22" t="n">
+        <v>-1158</v>
+      </c>
+      <c r="G167" s="22" t="n">
+        <v>6434</v>
+      </c>
+      <c r="I167" s="22" t="n">
+        <v>-3717</v>
+      </c>
+      <c r="K167" s="22" t="n">
+        <v>3293</v>
+      </c>
+      <c r="M167" s="22" t="n">
+        <v>-1841</v>
+      </c>
+      <c r="T167" s="22" t="n">
+        <v>3230</v>
+      </c>
+      <c r="U167" s="22" t="n">
+        <v>5205</v>
+      </c>
+      <c r="V167" s="22" t="n">
+        <v>-1158</v>
+      </c>
+      <c r="W167" s="22" t="n">
+        <v>-3717</v>
+      </c>
+      <c r="X167" s="22" t="n">
+        <v>-1841</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="20" t="inlineStr">
+        <is>
+          <t>신규 연결 현금성자산 증가</t>
+        </is>
+      </c>
+      <c r="C168" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V168" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="20" t="inlineStr">
+        <is>
           <t>연결 제외 현금성자산 감소</t>
         </is>
       </c>
-      <c r="C162" s="22" t="n">
+      <c r="C169" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E162" s="22" t="n">
+      <c r="E169" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T162" s="22" t="n">
+      <c r="T169" s="22" t="n">
         <v>-0</v>
       </c>
-      <c r="U162" s="22" t="n">
+      <c r="U169" s="22" t="n">
         <v>-9</v>
       </c>
-      <c r="V162" s="22" t="n">
+      <c r="V169" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9089,7 +9532,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -10491,7 +10934,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -10543,7 +10986,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -10595,7 +11038,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -10647,7 +11090,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -10699,7 +11142,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -10751,7 +11194,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -10803,7 +11246,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -10813,43 +11256,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -10873,7 +11316,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -10925,7 +11368,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -10977,7 +11420,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -11029,7 +11472,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -11081,7 +11524,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -11133,7 +11576,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -11203,7 +11646,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -11255,7 +11698,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -11265,49 +11708,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -11317,49 +11760,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -11369,49 +11812,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -11421,43 +11864,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -11481,7 +11924,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -11533,7 +11976,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -11585,7 +12028,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -11637,7 +12080,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -13681,24 +14124,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
